--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIX/LTAIPT_A63F39C.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIX/LTAIPT_A63F39C.xlsx
@@ -8,13 +8,17 @@
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
+    <sheet name="Hidden_1" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="Hidden_17">Hidden_1!$A$1:$A$2</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="85">
   <si>
     <t>49008</t>
   </si>
@@ -40,6 +44,9 @@
     <t>4</t>
   </si>
   <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
@@ -67,6 +74,9 @@
     <t>436963</t>
   </si>
   <si>
+    <t>571944</t>
+  </si>
+  <si>
     <t>436951</t>
   </si>
   <si>
@@ -109,6 +119,9 @@
     <t>Segundo apellido</t>
   </si>
   <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/01/2023 -&gt; Sexo (catálogo)</t>
+  </si>
+  <si>
     <t>Cargo o puesto que ocupa en el sujeto obligado</t>
   </si>
   <si>
@@ -130,7 +143,7 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t>González</t>
@@ -139,118 +152,127 @@
     <t>Betancour</t>
   </si>
   <si>
-    <t>Vocal I</t>
+    <t/>
   </si>
   <si>
     <t>transparencia@cobatlaxcala.edu.mx</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>Maximo Oscar</t>
-  </si>
-  <si>
-    <t>Luna</t>
-  </si>
-  <si>
-    <t>Capilla</t>
-  </si>
-  <si>
-    <t>Contralor Interno</t>
-  </si>
-  <si>
-    <t>contraloria@cobatlaxcala.edu.mx</t>
-  </si>
-  <si>
-    <t>Oscar</t>
-  </si>
-  <si>
-    <t>Lobatón</t>
-  </si>
-  <si>
-    <t>Corona</t>
-  </si>
-  <si>
-    <t>Subdirector Juridico</t>
-  </si>
-  <si>
-    <t>Vocal II</t>
-  </si>
-  <si>
-    <t>juridico@cobatlaxcala.edu.mx</t>
-  </si>
-  <si>
-    <t>Carlos Francisco</t>
-  </si>
-  <si>
-    <t>Fernandez</t>
-  </si>
-  <si>
-    <t>Salas</t>
-  </si>
-  <si>
-    <t>Director Administrativo</t>
-  </si>
-  <si>
-    <t>Secretario</t>
-  </si>
-  <si>
-    <t>diradmon@cobatlaxcala.edu.mx</t>
-  </si>
-  <si>
-    <t>Darwin</t>
-  </si>
-  <si>
-    <t>Director General</t>
-  </si>
-  <si>
-    <t>Presidente</t>
-  </si>
-  <si>
-    <t>dir.general@cobatlaxcala.edu.mx</t>
-  </si>
-  <si>
-    <t>D9830D7B74F18AA953CD85C797696F47</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>30/09/2022</t>
-  </si>
-  <si>
-    <t>Eduardo Antonio</t>
-  </si>
-  <si>
-    <t>Jefe de Materia</t>
+    <t>Bautista</t>
+  </si>
+  <si>
+    <t>Hernández</t>
+  </si>
+  <si>
+    <t>sistemas@cobatlaxcala.edu.mx</t>
+  </si>
+  <si>
+    <t>Pérez</t>
+  </si>
+  <si>
+    <t>Hombre</t>
+  </si>
+  <si>
+    <t>Lic. Eduardo Antonio</t>
+  </si>
+  <si>
+    <t>D09ED46F2FB5BA4BA8C52248A3FF00BE</t>
+  </si>
+  <si>
+    <t>01/07/2023</t>
+  </si>
+  <si>
+    <t>30/09/2023</t>
+  </si>
+  <si>
+    <t>Lic. Jose Humberto</t>
+  </si>
+  <si>
+    <t>Cuellar</t>
+  </si>
+  <si>
+    <t>Jefe del Departamento de Recursos Materiales</t>
+  </si>
+  <si>
+    <t>Vocal I del Comité</t>
+  </si>
+  <si>
+    <t>Rec.Materiales@cobatlaxcala.edu.mx</t>
+  </si>
+  <si>
+    <t>Área de Transparencia</t>
+  </si>
+  <si>
+    <t>28/07/2023</t>
+  </si>
+  <si>
+    <t>11/09/2023</t>
+  </si>
+  <si>
+    <t>AC1EC24FF2773248E2543D09D156FBB8</t>
+  </si>
+  <si>
+    <t>Ing. Jose Alberto</t>
+  </si>
+  <si>
+    <t>Responsable de Sistemas y Organización</t>
+  </si>
+  <si>
+    <t>Vocal II del Comité</t>
+  </si>
+  <si>
+    <t>98B62FBA3F34482DA50DE70FB08A5B92</t>
+  </si>
+  <si>
+    <t>Lic. Antonio Heber</t>
+  </si>
+  <si>
+    <t>García</t>
+  </si>
+  <si>
+    <t>Mendez</t>
+  </si>
+  <si>
+    <t>Integrante de la Dirección Academica</t>
+  </si>
+  <si>
+    <t>Vocal III del Comité</t>
+  </si>
+  <si>
+    <t>Dir.Academica@cobatlaxcala.edu.mx</t>
+  </si>
+  <si>
+    <t>D0EE233284040BC081957A886D67784C</t>
+  </si>
+  <si>
+    <t>Lic. Jorge</t>
+  </si>
+  <si>
+    <t>Martínez</t>
+  </si>
+  <si>
+    <t>Herman</t>
+  </si>
+  <si>
+    <t>Jefe del Departamento de Inventarios</t>
+  </si>
+  <si>
+    <t>Presidente del Comité</t>
+  </si>
+  <si>
+    <t>Inventarios@cobatlaxcala.edu.mx</t>
+  </si>
+  <si>
+    <t>DA0D668D75C2851FFF30FBC79EA65742</t>
   </si>
   <si>
     <t>Responsable de la Unidad de Transparencia</t>
   </si>
   <si>
-    <t>Unidad de Transparencia</t>
-  </si>
-  <si>
-    <t>16/11/2022</t>
-  </si>
-  <si>
-    <t>AFBF1AF3763FE8908852BAA1A0558FC5</t>
-  </si>
-  <si>
-    <t>B0EFA93BC4EC272C8FB0A18176EF6378</t>
-  </si>
-  <si>
-    <t>89288082AF5C68E455AC0B74F4EE2CEE</t>
-  </si>
-  <si>
-    <t>E650CD515C5CD6E4FEA59E3700E65230</t>
-  </si>
-  <si>
-    <t>Pérez Y</t>
-  </si>
-  <si>
-    <t>Pérez</t>
+    <t>Secretario del Comité</t>
+  </si>
+  <si>
+    <t>Mujer</t>
   </si>
 </sst>
 </file>
@@ -643,31 +665,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.28515625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="40.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="55.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="35.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="58.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="40.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="55.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -684,7 +707,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -699,7 +722,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -719,7 +742,7 @@
         <v>6</v>
       </c>
       <c r="H4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I4" t="s">
         <v>6</v>
@@ -728,62 +751,68 @@
         <v>6</v>
       </c>
       <c r="K4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L4" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" t="s">
         <v>7</v>
-      </c>
-      <c r="M4" t="s">
-        <v>9</v>
       </c>
       <c r="N4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="O4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="O5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -798,271 +827,290 @@
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
-    </row>
-    <row r="7" spans="1:14" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="O6" s="4"/>
+    </row>
+    <row r="7" spans="1:15" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>46</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="J9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="K9" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="J10" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="M9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N9" s="2" t="s">
+      <c r="K10" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F10" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="J11" s="2" t="s">
+      <c r="I12" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L12" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="K11" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="M12" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H12" s="2" t="s">
+      <c r="N12" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I12" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>43</v>
+      <c r="O12" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:N6"/>
+    <mergeCell ref="A6:O6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -1070,6 +1118,31 @@
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:I3"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H8:H191">
+      <formula1>Hidden_17</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>